--- a/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>PIK</t>
   </si>
@@ -656,90 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44282</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44009</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43918</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -747,149 +751,158 @@
         <v>3400</v>
       </c>
       <c r="E8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F8" s="3">
         <v>4000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1400</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -908,8 +921,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -958,8 +972,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1008,8 +1025,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1058,8 +1078,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,11 +1128,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1125,108 +1151,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7000</v>
       </c>
       <c r="K17" s="3">
         <v>7000</v>
       </c>
       <c r="L17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-900</v>
       </c>
       <c r="P18" s="3">
         <v>-900</v>
       </c>
       <c r="Q18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,8 +1278,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1266,17 +1300,17 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1290,63 +1324,69 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
-        <v>-800</v>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>-800</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1369,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
@@ -1384,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1392,61 +1432,67 @@
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E23" s="3">
         <v>-2000</v>
       </c>
       <c r="F23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-1000</v>
       </c>
       <c r="P23" s="3">
         <v>-1000</v>
       </c>
       <c r="Q23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1456,8 +1502,8 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1492,11 +1538,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1545,108 +1594,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E26" s="3">
         <v>-2000</v>
       </c>
       <c r="F26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-1000</v>
       </c>
       <c r="P26" s="3">
         <v>-1000</v>
       </c>
       <c r="Q26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E27" s="3">
         <v>-2000</v>
       </c>
       <c r="F27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1000</v>
       </c>
       <c r="P27" s="3">
         <v>-1000</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1695,8 +1753,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1745,8 +1806,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1795,8 +1859,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1845,8 +1912,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1866,17 +1936,17 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1890,63 +1960,69 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E33" s="3">
         <v>-2000</v>
       </c>
       <c r="F33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1000</v>
       </c>
       <c r="P33" s="3">
         <v>-1000</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1995,113 +2071,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E35" s="3">
         <v>-2000</v>
       </c>
       <c r="F35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1000</v>
       </c>
       <c r="P35" s="3">
         <v>-1000</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44282</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44009</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43918</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2120,8 +2205,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2140,40 +2226,41 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>200</v>
       </c>
       <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>200</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
@@ -2190,8 +2277,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2240,22 +2330,25 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
@@ -2264,17 +2357,17 @@
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2290,41 +2383,44 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E44" s="3">
         <v>9800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2340,41 +2436,44 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
         <v>900</v>
       </c>
       <c r="F45" s="3">
+        <v>900</v>
+      </c>
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2390,41 +2489,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E46" s="3">
         <v>11000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2440,8 +2542,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2490,40 +2595,43 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1500</v>
       </c>
       <c r="F48" s="3">
         <v>1500</v>
       </c>
       <c r="G48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2540,8 +2648,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2572,8 +2683,8 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2590,8 +2701,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2640,8 +2754,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2690,8 +2807,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2740,8 +2860,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2790,41 +2913,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E54" s="3">
         <v>12300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2840,8 +2966,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2860,8 +2989,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2880,41 +3010,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,13 +3061,16 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="E58" s="3">
         <v>2100</v>
@@ -2951,20 +3085,20 @@
         <v>2100</v>
       </c>
       <c r="I58" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J58" s="3">
         <v>2200</v>
       </c>
       <c r="K58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L58" s="3">
         <v>4500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,41 +3114,44 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
       </c>
       <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1700</v>
       </c>
       <c r="K59" s="3">
         <v>1700</v>
       </c>
       <c r="L59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3030,41 +3167,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3220,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3110,11 +3253,11 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3130,8 +3273,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3139,23 +3285,23 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
       </c>
       <c r="G62" s="3">
         <v>1100</v>
       </c>
       <c r="H62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3314,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3180,8 +3326,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3230,8 +3379,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3280,8 +3432,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3330,41 +3485,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3538,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3400,8 +3561,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3450,8 +3612,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3500,8 +3665,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3550,8 +3718,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3600,41 +3771,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-45500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-43500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-41500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-37300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-35700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3650,8 +3824,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3700,8 +3877,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3750,8 +3930,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3800,41 +3983,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3850,8 +4036,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3900,113 +4089,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44282</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44009</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43918</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E81" s="3">
         <v>-2000</v>
       </c>
       <c r="F81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1000</v>
       </c>
       <c r="P81" s="3">
         <v>-1000</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4025,8 +4223,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4054,8 +4253,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -4063,20 +4262,23 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4125,8 +4327,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4175,8 +4380,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4225,8 +4433,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4275,8 +4486,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4325,8 +4539,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4334,49 +4551,52 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4395,8 +4615,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4404,11 +4625,11 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -4427,17 +4648,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4445,8 +4666,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4495,8 +4719,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4545,8 +4772,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4554,11 +4784,11 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -4574,8 +4804,8 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4583,11 +4813,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4595,8 +4825,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4615,8 +4848,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4665,8 +4899,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4715,8 +4952,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4765,8 +5005,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4815,8 +5058,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4833,40 +5079,43 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>1900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4915,8 +5164,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4924,45 +5176,48 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-3000</v>
       </c>
       <c r="I102" s="3">
         <v>-3000</v>
       </c>
       <c r="J102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K102" s="3">
         <v>8100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>PIK</t>
   </si>
@@ -656,253 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44282</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3400</v>
+        <v>2200</v>
       </c>
       <c r="E8" s="3">
         <v>3400</v>
       </c>
       <c r="F8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H8" s="3">
         <v>4000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2300</v>
       </c>
       <c r="M9" s="3">
         <v>2200</v>
       </c>
       <c r="N9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P9" s="3">
         <v>2100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1400</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +947,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -975,8 +1002,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1028,8 +1061,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1081,8 +1120,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,11 +1176,17 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1152,114 +1203,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6500</v>
       </c>
       <c r="H17" s="3">
         <v>6000</v>
       </c>
       <c r="I17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1200</v>
       </c>
       <c r="N18" s="3">
         <v>-1400</v>
       </c>
       <c r="O18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1279,8 +1344,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1303,20 +1370,20 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1327,74 +1394,86 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E21" s="3">
-        <v>-2000</v>
+        <v>-4000</v>
       </c>
       <c r="F21" s="3">
         <v>-1900</v>
       </c>
       <c r="G21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1412,13 +1491,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
@@ -1427,72 +1506,84 @@
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1505,11 +1596,11 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1541,11 +1632,17 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1597,114 +1694,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1756,8 +1871,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1809,8 +1930,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1862,8 +1989,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1915,8 +2048,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1939,20 +2078,20 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -1963,66 +2102,78 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2074,119 +2225,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44282</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2206,8 +2375,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2227,47 +2398,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
         <v>200</v>
       </c>
       <c r="F41" s="3">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2280,8 +2453,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2333,8 +2512,14 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2345,34 +2530,34 @@
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>400</v>
+      </c>
+      <c r="O43" s="3">
+        <v>300</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2386,47 +2571,53 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F44" s="3">
         <v>8800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>11100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>12600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>14300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>12800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>12300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>11600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>8600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2439,8 +2630,14 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2448,38 +2645,38 @@
         <v>700</v>
       </c>
       <c r="E45" s="3">
+        <v>800</v>
+      </c>
+      <c r="F45" s="3">
+        <v>700</v>
+      </c>
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1600</v>
       </c>
       <c r="K45" s="3">
         <v>1700</v>
       </c>
       <c r="L45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,47 +2689,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F46" s="3">
         <v>9700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>15800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>22100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2748,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2598,46 +2807,52 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2651,8 +2866,14 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2686,11 +2907,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2704,8 +2925,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2757,8 +2984,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2810,8 +3043,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2863,8 +3102,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2916,47 +3161,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F54" s="3">
         <v>10900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>22200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2969,8 +3220,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2990,8 +3247,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3011,46 +3270,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4100</v>
       </c>
       <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>3500</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3064,19 +3325,25 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
-        <v>2100</v>
-      </c>
       <c r="F58" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
         <v>2100</v>
@@ -3088,23 +3355,23 @@
         <v>2100</v>
       </c>
       <c r="J58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,47 +3384,53 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,47 +3443,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3502,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3256,14 +3541,14 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3276,38 +3561,44 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3317,11 +3608,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3329,8 +3620,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3382,8 +3679,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3435,8 +3738,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3488,47 +3797,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F66" s="3">
         <v>6000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3541,8 +3856,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3562,8 +3883,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3615,8 +3938,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3668,8 +3997,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3721,8 +4056,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3774,47 +4115,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-51400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-47400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-45500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-43500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-41500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-39700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-37300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-35700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-33900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-32100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-30900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3827,8 +4174,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3880,8 +4233,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3933,8 +4292,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3986,47 +4351,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4039,8 +4410,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4092,119 +4469,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44282</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4224,8 +4619,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4256,29 +4653,35 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4330,8 +4733,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4383,8 +4792,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4436,8 +4851,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4489,8 +4910,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4542,61 +4969,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-2600</v>
       </c>
       <c r="J89" s="3">
         <v>-2200</v>
       </c>
       <c r="K89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4616,8 +5055,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4628,14 +5069,14 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4651,26 +5092,32 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4722,8 +5169,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4775,8 +5228,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4787,14 +5246,14 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -4807,29 +5266,35 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4849,8 +5314,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4902,8 +5369,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4955,8 +5428,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5008,8 +5487,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5061,13 +5546,19 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -5082,40 +5573,46 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>13500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5167,57 +5664,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>PIK</t>
   </si>
@@ -656,109 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44282</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3400</v>
       </c>
       <c r="F8" s="3">
         <v>3400</v>
@@ -767,167 +771,176 @@
         <v>3400</v>
       </c>
       <c r="H8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I8" s="3">
         <v>4000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1400</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -949,8 +962,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1008,8 +1022,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1067,8 +1084,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1126,8 +1146,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,11 +1205,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1205,126 +1231,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>7000</v>
       </c>
       <c r="N17" s="3">
         <v>7000</v>
       </c>
       <c r="O17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-900</v>
       </c>
       <c r="S18" s="3">
         <v>-900</v>
       </c>
       <c r="T18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1346,8 +1379,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1376,17 +1410,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1400,83 +1434,89 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
-        <v>-800</v>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
+      <c r="T21" s="3">
+        <v>-800</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1497,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
@@ -1512,7 +1552,7 @@
         <v>200</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1520,70 +1560,76 @@
       <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>100</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-2000</v>
       </c>
       <c r="H23" s="3">
         <v>-2000</v>
       </c>
       <c r="I23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1000</v>
       </c>
       <c r="S23" s="3">
         <v>-1000</v>
       </c>
       <c r="T23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1602,8 +1648,8 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1638,11 +1684,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1700,126 +1749,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-2000</v>
       </c>
       <c r="H26" s="3">
         <v>-2000</v>
       </c>
       <c r="I26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1000</v>
       </c>
       <c r="S26" s="3">
         <v>-1000</v>
       </c>
       <c r="T26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-2000</v>
       </c>
       <c r="H27" s="3">
         <v>-2000</v>
       </c>
       <c r="I27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1000</v>
       </c>
       <c r="S27" s="3">
         <v>-1000</v>
       </c>
       <c r="T27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1877,8 +1935,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1936,8 +1997,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1995,8 +2059,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2054,8 +2121,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2084,17 +2154,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2108,72 +2178,78 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-2000</v>
       </c>
       <c r="H33" s="3">
         <v>-2000</v>
       </c>
       <c r="I33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1000</v>
       </c>
       <c r="S33" s="3">
         <v>-1000</v>
       </c>
       <c r="T33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2231,131 +2307,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-2000</v>
       </c>
       <c r="H35" s="3">
         <v>-2000</v>
       </c>
       <c r="I35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1000</v>
       </c>
       <c r="S35" s="3">
         <v>-1000</v>
       </c>
       <c r="T35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44282</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2377,8 +2462,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2400,8 +2486,9 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2409,40 +2496,40 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
-      </c>
-      <c r="N41" s="3">
-        <v>200</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>200</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2459,8 +2546,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2518,8 +2608,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2527,22 +2620,22 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
@@ -2551,17 +2644,17 @@
         <v>200</v>
       </c>
       <c r="M43" s="3">
+        <v>200</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,50 +2670,53 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,8 +2732,11 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2645,41 +2744,41 @@
         <v>700</v>
       </c>
       <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>900</v>
       </c>
       <c r="H45" s="3">
         <v>900</v>
       </c>
       <c r="I45" s="3">
+        <v>900</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,50 +2794,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2754,8 +2856,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2813,49 +2918,52 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1500</v>
       </c>
       <c r="I48" s="3">
         <v>1500</v>
       </c>
       <c r="J48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2872,8 +2980,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2913,8 +3024,8 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2931,8 +3042,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2990,8 +3104,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3049,8 +3166,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3108,8 +3228,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3167,50 +3290,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3352,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3249,8 +3378,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3272,8 +3402,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3281,41 +3412,41 @@
         <v>3800</v>
       </c>
       <c r="E57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,22 +3462,25 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>900</v>
       </c>
       <c r="F58" s="3">
         <v>900</v>
       </c>
       <c r="G58" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="H58" s="3">
         <v>2100</v>
@@ -3361,20 +3495,20 @@
         <v>2100</v>
       </c>
       <c r="L58" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="M58" s="3">
         <v>2200</v>
       </c>
       <c r="N58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O58" s="3">
         <v>4500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3390,50 +3524,53 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1000</v>
       </c>
       <c r="J59" s="3">
         <v>1000</v>
       </c>
       <c r="K59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1700</v>
       </c>
       <c r="N59" s="3">
         <v>1700</v>
       </c>
       <c r="O59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3449,50 +3586,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E60" s="3">
         <v>5800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,8 +3648,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3547,11 +3690,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3567,41 +3710,44 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>900</v>
       </c>
       <c r="G62" s="3">
         <v>900</v>
       </c>
       <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
         <v>1000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>1100</v>
       </c>
       <c r="K62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3614,8 +3760,8 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -3626,8 +3772,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3685,8 +3834,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3744,8 +3896,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3803,50 +3958,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +4020,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3885,8 +4046,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3944,8 +4106,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4003,8 +4168,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4062,8 +4230,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4121,50 +4292,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-53200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-51400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-47400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-41500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-37300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-35700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-32100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4354,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4239,8 +4416,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4298,8 +4478,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4357,50 +4540,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4416,8 +4602,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4475,131 +4664,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44282</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-2000</v>
       </c>
       <c r="H81" s="3">
         <v>-2000</v>
       </c>
       <c r="I81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1000</v>
       </c>
       <c r="S81" s="3">
         <v>-1000</v>
       </c>
       <c r="T81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4621,8 +4819,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4659,8 +4858,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4668,20 +4867,23 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4739,8 +4941,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4798,8 +5003,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4857,8 +5065,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4916,8 +5127,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4975,67 +5189,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-100</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
       </c>
       <c r="H89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5057,8 +5277,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5075,11 +5296,11 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -5098,17 +5319,17 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5116,8 +5337,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5175,8 +5399,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5234,8 +5461,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5252,11 +5482,11 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -5272,8 +5502,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -5281,11 +5511,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5293,8 +5523,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5316,8 +5549,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5375,8 +5609,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5434,8 +5671,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5493,8 +5733,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5552,17 +5795,20 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -5579,40 +5825,43 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>1900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5670,63 +5919,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-3000</v>
       </c>
       <c r="L102" s="3">
         <v>-3000</v>
       </c>
       <c r="M102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N102" s="3">
         <v>8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PIK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>PIK</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44282</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3400</v>
       </c>
       <c r="G8" s="3">
         <v>3400</v>
@@ -774,111 +778,117 @@
         <v>3400</v>
       </c>
       <c r="I8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J8" s="3">
         <v>4000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3400</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
-        <v>3900</v>
-      </c>
       <c r="G9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1400</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,61 +896,64 @@
         <v>700</v>
       </c>
       <c r="E10" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="F10" s="3">
-        <v>-500</v>
+        <v>1600</v>
       </c>
       <c r="G10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3500</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3400</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2000</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -963,8 +976,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1025,8 +1039,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1087,31 +1104,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>2900</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1149,8 +1169,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,11 +1231,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1232,132 +1258,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4000</v>
       </c>
-      <c r="F17" s="3">
-        <v>7400</v>
-      </c>
       <c r="G17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H17" s="3">
         <v>5300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>7000</v>
       </c>
       <c r="O17" s="3">
         <v>7000</v>
       </c>
       <c r="P17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1800</v>
-      </c>
       <c r="F18" s="3">
-        <v>-4000</v>
+        <v>-1700</v>
       </c>
       <c r="G18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2100</v>
       </c>
       <c r="I18" s="3">
         <v>-2000</v>
       </c>
       <c r="J18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-900</v>
       </c>
       <c r="T18" s="3">
         <v>-900</v>
       </c>
       <c r="U18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1380,31 +1413,32 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1413,17 +1447,17 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1437,75 +1471,81 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-4000</v>
-      </c>
       <c r="G21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
-        <v>-800</v>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
+      <c r="U21" s="3">
+        <v>-800</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1515,11 +1555,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1540,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
@@ -1555,7 +1595,7 @@
         <v>200</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -1563,73 +1603,79 @@
       <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-2000</v>
       </c>
       <c r="I23" s="3">
         <v>-2000</v>
       </c>
       <c r="J23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1000</v>
       </c>
       <c r="T23" s="3">
         <v>-1000</v>
       </c>
       <c r="U23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1651,8 +1697,8 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1687,11 +1733,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1752,132 +1801,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2000</v>
       </c>
       <c r="I26" s="3">
         <v>-2000</v>
       </c>
       <c r="J26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1000</v>
       </c>
       <c r="T26" s="3">
         <v>-1000</v>
       </c>
       <c r="U26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-2000</v>
       </c>
       <c r="I27" s="3">
         <v>-2000</v>
       </c>
       <c r="J27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1000</v>
       </c>
       <c r="T27" s="3">
         <v>-1000</v>
       </c>
       <c r="U27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1938,8 +1996,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2000,8 +2061,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2062,8 +2126,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2124,31 +2191,34 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2157,17 +2227,17 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2181,75 +2251,81 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-2000</v>
       </c>
       <c r="I33" s="3">
         <v>-2000</v>
       </c>
       <c r="J33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1000</v>
       </c>
       <c r="T33" s="3">
         <v>-1000</v>
       </c>
       <c r="U33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2310,137 +2386,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-2000</v>
       </c>
       <c r="I35" s="3">
         <v>-2000</v>
       </c>
       <c r="J35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1000</v>
       </c>
       <c r="T35" s="3">
         <v>-1000</v>
       </c>
       <c r="U35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44282</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2463,8 +2548,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2487,8 +2573,9 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2499,40 +2586,40 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
-      </c>
-      <c r="O41" s="3">
-        <v>200</v>
       </c>
       <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>200</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
@@ -2549,8 +2636,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2611,8 +2701,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2623,22 +2716,22 @@
         <v>100</v>
       </c>
       <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -2647,17 +2740,17 @@
         <v>200</v>
       </c>
       <c r="N43" s="3">
+        <v>200</v>
+      </c>
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2673,53 +2766,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8500</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,53 +2831,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>900</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2797,53 +2896,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,31 +2961,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2921,52 +3026,55 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1500</v>
       </c>
       <c r="J48" s="3">
         <v>1500</v>
       </c>
       <c r="K48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2983,8 +3091,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3027,8 +3138,8 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3045,8 +3156,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3107,8 +3221,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3169,31 +3286,34 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3231,8 +3351,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3293,53 +3416,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E54" s="3">
         <v>6300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,8 +3481,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3379,8 +3508,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3403,53 +3533,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3800</v>
+        <v>1700</v>
       </c>
       <c r="E57" s="3">
-        <v>3800</v>
+        <v>1700</v>
       </c>
       <c r="F57" s="3">
-        <v>3700</v>
+        <v>1800</v>
       </c>
       <c r="G57" s="3">
-        <v>3600</v>
+        <v>1900</v>
       </c>
       <c r="H57" s="3">
-        <v>3200</v>
+        <v>1900</v>
       </c>
       <c r="I57" s="3">
-        <v>3100</v>
+        <v>1700</v>
       </c>
       <c r="J57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3465,31 +3596,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>5000</v>
       </c>
       <c r="E58" s="3">
-        <v>1100</v>
+        <v>4600</v>
       </c>
       <c r="F58" s="3">
-        <v>900</v>
+        <v>3500</v>
       </c>
       <c r="G58" s="3">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="H58" s="3">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="I58" s="3">
-        <v>2100</v>
+        <v>3900</v>
       </c>
       <c r="J58" s="3">
-        <v>2100</v>
+        <v>3800</v>
       </c>
       <c r="K58" s="3">
         <v>2100</v>
@@ -3498,20 +3632,20 @@
         <v>2100</v>
       </c>
       <c r="M58" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="N58" s="3">
         <v>2200</v>
       </c>
       <c r="O58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P58" s="3">
         <v>4500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3527,53 +3661,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1000</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>1000</v>
       </c>
       <c r="L59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>800</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1700</v>
       </c>
       <c r="O59" s="3">
         <v>1700</v>
       </c>
       <c r="P59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,53 +3726,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,31 +3791,34 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3693,11 +3836,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3713,44 +3856,47 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1100</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>1100</v>
       </c>
       <c r="L62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3763,8 +3909,8 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -3775,8 +3921,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3837,8 +3986,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3899,8 +4051,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3961,53 +4116,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4023,8 +4181,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4047,8 +4208,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4109,8 +4271,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4171,8 +4336,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4233,8 +4401,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4295,53 +4466,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-53200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-43500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-37300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,8 +4531,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4419,8 +4596,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4481,8 +4661,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4543,53 +4726,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1400</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4605,8 +4791,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4667,137 +4856,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44282</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-2000</v>
       </c>
       <c r="I81" s="3">
         <v>-2000</v>
       </c>
       <c r="J81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1000</v>
       </c>
       <c r="T81" s="3">
         <v>-1000</v>
       </c>
       <c r="U81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4820,8 +5018,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4835,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -4861,8 +5060,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4870,20 +5069,23 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4944,8 +5146,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5006,8 +5211,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5068,8 +5276,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5130,8 +5341,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5192,70 +5406,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5278,19 +5498,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5299,11 +5520,11 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -5322,17 +5543,17 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5340,8 +5561,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5402,8 +5626,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5464,19 +5691,22 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -5485,11 +5715,11 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -5505,8 +5735,8 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5514,11 +5744,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5526,8 +5756,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5550,31 +5783,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5612,8 +5846,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5674,8 +5911,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5736,8 +5976,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5798,93 +6041,99 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5922,8 +6171,11 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5931,57 +6183,60 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-3000</v>
       </c>
       <c r="M102" s="3">
         <v>-3000</v>
       </c>
       <c r="N102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O102" s="3">
         <v>8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
